--- a/docs/QA-Checklist-DataTrust-Nibras.xlsx
+++ b/docs/QA-Checklist-DataTrust-Nibras.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Trust" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nibras" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enterprise QA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data Trust'!$A$2:$N$21</definedName>
@@ -518,8 +519,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
@@ -528,11 +527,9 @@
           <t>HOW TO USE</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
           <t>1. Act as the relevant user</t>
@@ -545,7 +542,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
           <t>2. Status meanings</t>
@@ -558,7 +554,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
           <t>3. Severity (on Fail only)</t>
@@ -571,7 +566,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
           <t>4. Action</t>
@@ -584,7 +578,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
           <t>5. Priority</t>
@@ -597,7 +590,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
           <t>6. Journey Steps</t>
@@ -610,8 +602,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
@@ -620,11 +610,9 @@
           <t>SHEETS</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Data Trust</t>
@@ -637,7 +625,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Nibras</t>
@@ -650,8 +637,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
@@ -660,11 +645,9 @@
           <t>EXCLUDED (still under dev)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Pulse / AI console</t>
@@ -821,7 +804,7 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>/connections → /connections/:id → /catalog/metadata</t>
+          <t>/catalog/connections → /catalog/connections/:id → /catalog/metadata</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -831,7 +814,7 @@
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
@@ -844,12 +827,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="8" t="inlineStr"/>
-      <c r="M3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>Layer 4 browser walk: 2 DB sources (Probe DB2/DB3, database, active); /connections/sources + /consuming = 200. FINDING (Low): "New Connection" dialog only exposes Name/Slug/Source Type/Description — no host/credentials fields to onboard a real source. FINDING (Low): "Test" shows "Connection test successful" but the status badge stays "Not Tested" (state not persisted). FIXED (cycle 2): New Connection dialog now renders conditional config fields per source type (database→Host/Port/Database Name/Username/Password; api→Base URL/API Key; mdm→Base URL/API Key; iot→Endpoint/API Key; excel/manual→File Path). Backend test_connection now persists last_test_status="success"/"failure" + status="active"/"error" + last_tested_at. Browser-verified: API-type dialog shows Base URL/API Key; Database shows Host/Port/Database Name/Username/Password; "Probe DB2" shows "Connected" badge; POST /connections/sources/1/test/ returns success + re-read persists status. Regression test test_connection_service.py added.</t>
+        </is>
+      </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fixed + re-verified (cycle 2)</t>
         </is>
       </c>
     </row>
@@ -895,7 +890,7 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
@@ -905,12 +900,24 @@
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K4" s="10" t="inlineStr"/>
-      <c r="L4" s="10" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>CORRECTED (prior "catalog/datasets=0" was wrong): 6 Data Products registered — EPH6C Demo, DP3 Transport, Smart Village, Abu Qir, South Valley, aaa. Smart Village has 4 tables: Monthly Water (18 rows), Monthly Electricity (26), Monthly Chilled Water (20), GHG Inventory (54). Data Products UI + datasets CRUD wired (200); full publish→discover journey not re-exercised.</t>
+        </is>
+      </c>
       <c r="N4" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -959,7 +966,7 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -972,9 +979,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="8" t="inlineStr"/>
-      <c r="M5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>/catalog/search/?q=emission = 200 {query,total,results}; 57 assets, 3 domains, 9 tags; Catalog Studio renders (Search, Asset Profiles, Governance).</t>
+        </is>
+      </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -1022,7 +1041,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -1035,9 +1054,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr"/>
-      <c r="L6" s="10" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>dataschema 11 tables / 46 fields / 260 rows; tables/fields/rows/schema-logs endpoints 200.</t>
+        </is>
+      </c>
       <c r="N6" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -1074,7 +1105,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>/carbon-api/evidence/</t>
+          <t>/catalog/mdm → /admin/org-units → /admin/org-units/:id</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -1084,7 +1115,7 @@
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -1094,12 +1125,24 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr"/>
-      <c r="L7" s="8" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr"/>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>evidence/ = 0 (no artifacts yet); POST empty = 400 (validation, correct — not 500). Feature wired, not exercised.</t>
+        </is>
+      </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -1148,7 +1191,7 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
@@ -1161,9 +1204,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr"/>
-      <c r="L8" s="10" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>9 DQ rules, 32 results, 7 table-profiles; /dq/rules|jobs|results|table-profiles = 200.</t>
+        </is>
+      </c>
       <c r="N8" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -1211,7 +1266,7 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -1224,9 +1279,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr"/>
-      <c r="L9" s="8" t="inlineStr"/>
-      <c r="M9" s="8" t="inlineStr"/>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>18 org-units, 9 reference-sets, 61 reference-values; MDM endpoints 200; Master Data UI entry present.</t>
+        </is>
+      </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -1274,7 +1341,7 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -1287,9 +1354,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K10" s="10" t="inlineStr"/>
-      <c r="L10" s="10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>my-data = 5 modules / 260 rows; UI grid renders (Scope/Status filters, DQ%, Last Entry, Open workspace). Data Entry workspace loads.</t>
+        </is>
+      </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -1337,7 +1416,7 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -1350,9 +1429,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr"/>
-      <c r="L11" s="8" t="inlineStr"/>
-      <c r="M11" s="8" t="inlineStr"/>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>9 factors, 8 GWP, 8 calculation rules; Config sidebar (Emission Factors, Calculation Rules, Boundaries, Base Years, Inventory Coverage) present.</t>
+        </is>
+      </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -1399,7 +1490,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -1409,15 +1500,27 @@
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K12" s="10" t="inlineStr"/>
-      <c r="L12" s="10" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>115 calculations; /calculations/summary rich (by_scope/by_status/by_module, latest_run_at). FINDING (Fixed): /carbon/calculations crashed on load with TypeError "Cannot read properties of undefined (reading 'size')" (MUI X DataGrid v8 selection API mismatch — v7 array rowSelectionModel). Migrated to v8 Set-based {type,ids} model; grid now renders Scope 1/2 Draft runs with Recalculate buttons. verifications=0 (sign-off not exercised). Refinement (Fixed+Verified): the first v8 fix replaced checkboxSelection with rowSelection:true, which in v8 community DataGrid DISABLES multi-select (isMultipleRowSelectionEnabled requires checkboxSelection) and hides the checkbox column. Restored checkboxSelection + disableRowSelectionOnClick with the Set-based rowSelectionModel. Browser-verified: admin checkbox column renders; multi-select works (“Recalculate Selected (2)” + “2 rows selected”, no v8 crash).</t>
+        </is>
+      </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fixed + re-verified (cycle 2)</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1564,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -1474,9 +1577,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr"/>
-      <c r="L13" s="8" t="inlineStr"/>
-      <c r="M13" s="8" t="inlineStr"/>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>3 SBTi targets, 1 base-year, 2 boundaries, 2 coverage-goals; SBTi Targets UI entry present.</t>
+        </is>
+      </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -1524,7 +1639,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
@@ -1537,9 +1652,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K14" s="10" t="inlineStr"/>
-      <c r="L14" s="10" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>/carbon/report/ rich (title, generated_at, summary, scope_details, by_gas, org_unit_rollup, rows); Reports UI entry present.</t>
+        </is>
+      </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -1586,7 +1713,7 @@
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
@@ -1599,9 +1726,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="8" t="inlineStr"/>
-      <c r="M15" s="8" t="inlineStr"/>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>/carbon/chairman/ rich (headline, scope_breakdown, coverage_by_campus, sbti, trajectory); /carbon/dashboard/ totals; Chairman Overview + Emissions Dashboard UI.</t>
+        </is>
+      </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -1650,7 +1789,7 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
@@ -1660,15 +1799,27 @@
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K16" s="10" t="inlineStr"/>
-      <c r="L16" s="10" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>49 users (owner1/admin2/auditor2/analyst1/owner2/schemauser2/…), 19 groups (admin/admins_group/analysts_group/auditors_group/carbon_analysts_group), New User + New Group actions render. Role Registry (/admin/role-matrix) shows Carbon Footprint 3 roles v1.0.0 (carbon:data_owner, carbon:analyst, carbon:admin), Data Catalog 1 role, Data Quality 1 role, Connections/Import-Export/Data Schema 0 roles. FINDING (Low): alamein.* data-owner users (medical/finance/transport/hotels) have NO group/ScopedRole → my-data returns "No accessible org units" (restrictive default correct, but provisioning of scoped roles is incomplete). FIXED (cycle 2): new idempotent command provision_alamein_rbac.py creates 5 dept OrgUnits (Medicine/Financial Affairs/Transportation/Student Hotels/Educational Hospital) under Alamein Campus + provisions 5 users (alamein.admin→carbon_lead; alamein.medical→dataowners@Medicine+Hospital; alamein.finance; alamein.transport; alamein.hotels). API-verified: get_visible_org_units(alamein.transport)=[Transportation]; GET /carbon/my-data/ as alamein.transport → org_unit "Transportation / النقل". Browser-verified: login alamein.transport → /carbon/my-data renders "Transportation / النقل" (was "No accessible org units"). Regression test test_provision_alamein_rbac.py added.</t>
+        </is>
+      </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fixed + re-verified (cycle 2)</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1853,7 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>/admin/governance → /admin/catalog/field-policies</t>
+          <t>/catalog/policies → /admin/catalog/field-policies</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -1712,7 +1863,7 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
@@ -1725,9 +1876,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr"/>
-      <c r="L17" s="8" t="inlineStr"/>
-      <c r="M17" s="8" t="inlineStr"/>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>Layer 4 browser walk: Governance Policies (/catalog/policies) renders 4 active policies with Edit/Delete + "New Policy" — Protect Scope 1 Carbon Modules, Scope 1 Update Requires Review, Carbon Data Owner Protection, Verified Period Table Lock. Field Access Policies (/admin/catalog/field-policies) renders ID/Field/Label/Table/Type/Masking grid with search + "Refresh field policies" (fleet_fuel_log, Monthly Electricity/Chilled Water/Water, GHG Inventory fields; masking=None).</t>
+        </is>
+      </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -1774,7 +1937,7 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
@@ -1787,12 +1950,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K18" s="10" t="inlineStr"/>
-      <c r="L18" s="10" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>FINDING (Medium): /admin/audit renders filters (Action/User/From/To) + Refresh/Export CSV, but "Total Events: 0 / No audit logs found" despite heavy activity. Root cause: the Admin Audit Log page is wired to accounts/role-audit-logs/ (RoleAssignmentAuditLog only) via config.auditLogs, NOT the general RequestAuditLog (core) or CalculationAudit/ExportAudit/catalog governance events. The page claims "complete record of all system changes/user actions" but only surfaces role-assignment audit. FIXED+VERIFIED: rewired to core/audit-logs/ (new RequestAuditLogViewSet: id/user/ip_address/method/path/query_string/status_code/duration_ms/correlation_id/timestamp + RequestAuditLogFilter via django-filter). GET /carbon-api/core/audit-logs/ returns 3074 rows. Browser /admin/audit now renders Total Events 50 (Update 32 / Create 18) with real table rows, method→action chips, and Export CSV enabled.</t>
+        </is>
+      </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fixed + re-verified (cycle 2)</t>
         </is>
       </c>
     </row>
@@ -1827,7 +2002,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>/import-export → /imports</t>
+          <t>/catalog/importexport → /catalog/imports</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -1837,7 +2012,7 @@
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
@@ -1847,12 +2022,24 @@
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="inlineStr"/>
-      <c r="L19" s="8" t="inlineStr"/>
-      <c r="M19" s="8" t="inlineStr"/>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>Layer 4 browser walk: /catalog/importexport renders 3 tabs (Export Projects/Import Jobs/Export Jobs). Import Jobs tab shows "Upload Data File" (Target Table, Format=CSV, Data Source) + Choose File/Upload; empty jobs list. importexport/import = 0 jobs (endpoint 200). Bulk-import journey not exercised.</t>
+        </is>
+      </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -1890,7 +2077,7 @@
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>/import-export → /exports</t>
+          <t>/catalog/importexport → /catalog/exports</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -1900,7 +2087,7 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr">
@@ -1910,12 +2097,24 @@
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K20" s="10" t="inlineStr"/>
-      <c r="L20" s="10" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>Layer 4 browser walk: /catalog/exports renders Projects/Jobs tabs + "New Project" + Name/Format/Schedule/Actions table (empty). Export Jobs tab shows "No export jobs found". importexport/export + export-projects = 0 jobs (endpoints 200). Export journey not exercised.</t>
+        </is>
+      </c>
       <c r="N20" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -1963,7 +2162,7 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
@@ -1973,12 +2172,24 @@
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr"/>
-      <c r="L21" s="8" t="inlineStr"/>
-      <c r="M21" s="8" t="inlineStr"/>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t>Re-verified live: POST /carbon-api/token/ 200 (JWT), GET /carbon-api/integrations/turnkey/configs/ = 200, /links/ = 200. configs + links = 0 rows; config→predict→drift + callback routes present. ML journey not exercised end-to-end.</t>
+        </is>
+      </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -2154,7 +2365,7 @@
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
@@ -2164,12 +2375,24 @@
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="8" t="inlineStr"/>
-      <c r="M3" s="8" t="inlineStr"/>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>F1 grid height 0px (P3), F2 drawer overlap (P2), F3 enum capture (P3) — all fixed &amp; E2E re-verified.</t>
+        </is>
+      </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -2217,7 +2440,7 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
@@ -2230,9 +2453,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K4" s="10" t="inlineStr"/>
-      <c r="L4" s="10" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>F4 positions/org rendering issue — fixed &amp; re-verified.</t>
+        </is>
+      </c>
       <c r="N4" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -2280,7 +2515,7 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -2293,9 +2528,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="8" t="inlineStr"/>
-      <c r="M5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>F5 empty-state Add dialog, F6 compute 500, F7 backend down, F8 zero-salary seed — all fixed; full lifecycle Draft→Compute→Computed→Validate→Validated→Commit→Committed verified (run id=1).</t>
+        </is>
+      </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -2342,7 +2589,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -2355,9 +2602,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr"/>
-      <c r="L6" s="10" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>Was FAIL (F10 feature-gap); resolved via people/self_views.py; payslip self-service view verified.</t>
+        </is>
+      </c>
       <c r="N6" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -2405,7 +2664,7 @@
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -2418,9 +2677,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr"/>
-      <c r="L7" s="8" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr"/>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>F14 leave-status label verified; remaining findings resolved.</t>
+        </is>
+      </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -2468,7 +2739,7 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
@@ -2481,9 +2752,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr"/>
-      <c r="L8" s="10" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>Loan status sync fixed; end-to-end verified.</t>
+        </is>
+      </c>
       <c r="N8" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -2531,7 +2814,7 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -2544,9 +2827,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr"/>
-      <c r="L9" s="8" t="inlineStr"/>
-      <c r="M9" s="8" t="inlineStr"/>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>Manager inbox + FSM transitions verified.</t>
+        </is>
+      </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -2593,7 +2888,7 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -2606,9 +2901,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K10" s="10" t="inlineStr"/>
-      <c r="L10" s="10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>Clean pass (leave policy + attendance).</t>
+        </is>
+      </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -2655,7 +2962,7 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -2668,9 +2975,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr"/>
-      <c r="L11" s="8" t="inlineStr"/>
-      <c r="M11" s="8" t="inlineStr"/>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>Clean pass (certifications + rotation).</t>
+        </is>
+      </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -2718,7 +3037,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -2731,9 +3050,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K12" s="10" t="inlineStr"/>
-      <c r="L12" s="10" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>F20 org_unit required (was 500 IntegrityError) fixed + E2E verified (corr id=27); F21 archive action added + verified (corr 23 archived).</t>
+        </is>
+      </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -2780,7 +3111,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -2790,15 +3121,27 @@
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K13" s="8" t="inlineStr"/>
-      <c r="L13" s="8" t="inlineStr"/>
-      <c r="M13" s="8" t="inlineStr"/>
+          <t>Cosmetic</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>F22 role-assignment audit log written + endpoint /accounts/role-audit-logs/; F23 refetchTables 403 for HR-only user fixed (no dataschema/tables call post-fix). F24 residual (P3): role-audit-logs API omits 'actor' field.</t>
+        </is>
+      </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deferred</t>
         </is>
       </c>
     </row>
@@ -2843,7 +3186,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
@@ -2856,9 +3199,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K14" s="10" t="inlineStr"/>
-      <c r="L14" s="10" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>Compensation masked: emp_1001 → basic_salary stripped + /compensation/ 403; ahmed → 420.000 + 200. Audit: view_compensation events (latest id=45). civil_id blank in real data (structural client-side masking only).</t>
+        </is>
+      </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -2906,7 +3261,7 @@
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
@@ -2919,9 +3274,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="8" t="inlineStr"/>
-      <c r="M15" s="8" t="inlineStr"/>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>QA Validator</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>MDM 33 GOFSCO org units; DQ 16 people-domain rules; audit /catalog/governance-events/ = 45 events; no AASTMT/carbon leak (brand=nibras isolated).</t>
+        </is>
+      </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
           <t>—</t>
@@ -2949,4 +3316,704 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Enterprise Professional QA — Gap Analysis (Cycle 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Generated 2026-09-13 · Carbon Data Trust Platform (brand=aastmt) · beyond the 32 BP rows already at Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Gap / Risk</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Current State</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Recommended Action</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Performance / Load</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>No load or concurrency test evidence for DRF API or React SPA; large DataGrid datasets + 260→100k rows unknown.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>No k6/Locust artifacts; throttle user=1000/hr (dev-loose).</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Add k6/Locust scripts for /carbon/my-data, /dataschema/rows, /evidence/bulk-upload, /dq; set SLO (p95 &lt; 800ms) and test at 1k/5k/10k rows.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>P1 High</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>QA / DevOps</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Security scanning</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>No dependency/SAST/OWASP evidence; JWT + secrets posture unverified.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Audited (cycle 3): npm=20 vulns (2 low/6 moderate/12 high — vite&lt;=6.4.2, react-router, postcss, rollup, @babel/core, yaml); pip-audit=8 vulnerable (django 5.2.3, drf 3.16.0, simplejwt 5.5.0, sqlparse 0.5.3, python-dotenv 1.1.0, cryptography 44.0.0, pyjwt 2.9.0, mcp 1.19.0).</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Apply fixes: django-&gt;5.2.17, drf-&gt;3.17.2, simplejwt-&gt;5.5.1, sqlparse-&gt;0.5.4, python-dotenv-&gt;1.2.2, cryptography-&gt;44.0.1+, pyjwt-&gt;2.12.1, mcp-&gt;1.23.0+; npm audit fix (frontend); then bandit + semgrep + OWASP Top 10 pass.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>P0 Critical</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Security / DevOps</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Audited (cycle 3) — upgrades pending approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Backup / Restore &amp; DR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>No backup/restore drill for PostgreSQL, media/evidence files, or chroma_db.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>docker-compose + manage.sh have no backup job; evidence/ files not backed up.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>pg_dump cron + media/ + chroma_db/ backup; test restore quarterly; define RPO (&lt;=1h) / RTO (&lt;=4h); offsite copy.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>P0 Critical</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Monitoring / Alerting</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>No APM/error-tracking or alerting; backend errors only in logs/backend.log.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Console log-only; no Sentry/OTel; /ai/insights/stream/ WebSocket failing in browser console (ERR_ABORTED).</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Add Sentry (backend+frontend) + structured JSON logs + alert rules (error rate, latency, queue depth, disk).</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>P1 High</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Accessibility (WCAG 2.1 AA)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>No a11y audit; RTL (ar) layout unverified.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>i18n en/ar 3152 keys green, but no axe/Playwright a11y run; combobox/grid ARIA unverified.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Run axe-core + keyboard-only + screen-reader pass on /catalog, /carbon/my-data, /people/employees; verify RTL (ar) layout.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>P1 High</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Frontend / QA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Browser / device matrix</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Only Chromium verified; Safari/Firefox + mobile untested.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Playwright config exists (chromium default).</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Extend playwright to firefox+webkit + mobile viewports; run responsive smoke.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>P2 Medium</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Data migration / rollback</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Schema-change rollback + migration safety on prod-shaped data untested.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Migrations applied on carbon_dev only; no rollback drill.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Test forward+backward migrations on a copy; version seed scripts; add DB snapshot before deploy.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>P1 High</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Backend / DevOps</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rate limiting &amp; abuse</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Login throttling (1000/min) is dev-loose; brute-force lockout unverified.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>REST_FRAMEWORK throttle config dev values; no account lockout.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Tighten prod throttle (login ~5/min), add account lockout + IP allow/deny; test.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>P1 High</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Backend / Security</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Secrets management</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Hardcoded credentials in seed scripts + possibly .env committed.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdminPa_132 / Alamein_2026 removed from 11 committed source files (cycle 3): seed_alamein_full.py, seed_trust_core.py, seed_fields.py, seed_tables.py, provision_alamein_rbac.py, seed_aastmt_org.py, qa_zone_verify.py, qa_pulse_smoke.py, qa_pulse_smoke_nibras.py; now read CARBON_ADMIN_PASSWORD / ALAMEIN_USER_PASSWORD from gitignored backend/.env. Regression test updated + passing.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Run gitleaks/trufflehog repo scan; rotate JWT secret + LLM_API_KEY; add pre-commit secret-scan hook; remaining low-sev: transport/facilities officer test creds + deploy_aastmt banner + generate_checklist.py.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>P0 Critical</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Fixed (cycle 3) — scan pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>i18n completeness</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Date/number locale + RTL components untested; ar copy coverage of new strings.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>check-i18n-keys.js parity green (3152); no locale-aware date/number test.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Verify ar strings render + date/number locale in /carbon + /people; add ar screenshot review.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>P2 Medium</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Audit log unification</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>General vs role-assignment audit still split; calc/export/catalog events not unified.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DT-BP-016 rewired /admin/audit to core/audit-logs (3074 rows); CalculationAudit/ExportAudit/governance not merged.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Unify a single immutable audit stream (actor, action, target, before/after) across core/accounts/emissions/importexport.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>P1 High</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Data quality coverage</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Only 9 DQ rules; new Alamein tables show DQ 'Failing 0%' (no rules).</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>fleet_fuel_log renders DQ 0% (no rules configured for Alamein seed tables).</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Extend DQ rule set + table-profiles to Alamein modules; define freshness/completeness thresholds.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>P2 Medium</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DQ / Data</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Evidence pipeline hardening</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Virus scan, content-type sniffing, storage quota, retention for evidence files.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ext allowlist + 50MB cap present; no AV scan or retention policy.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Add AV scan on upload, strict MIME sniff, storage quota, retention/schedule; backup (see #3).</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>P2 Medium</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Backend / Security</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>API contract / OpenAPI drift</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Swagger may drift from actual DRF endpoints.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>/swagger/ present; not diffed against code.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generate + diff OpenAPI in CI (drf-spectacular); add contract tests.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>P2 Medium</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Test coverage &amp; e2e</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>pytest coverage unknown; critical e2e paths (payroll, calculations, evidence) manual.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8 role-audit + regression tests pass; no measured coverage; e2e suite partial.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Measure + raise coverage; add e2e for /carbon/my-data entry, payroll cycle, evidence upload in CI.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>P1 High</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>QA / Backend</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>